--- a/tools/importer/reports/import-students.report.xlsx
+++ b/tools/importer/reports/import-students.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-27T07:25:40.953Z</t>
+    <t>2026-08-27T07:58:41.076Z</t>
   </si>
   <si>
     <t>Current students - RMIT University</t>

--- a/tools/importer/reports/import-students.report.xlsx
+++ b/tools/importer/reports/import-students.report.xlsx
@@ -40,7 +40,7 @@
     <t>students.report.json</t>
   </si>
   <si>
-    <t>["hero-overlay","cards-links","columns-feature","cards-tile","cards-tile","cards-tile","cards-tile"]</t>
+    <t>["hero-overlay","cards-links","columns-feature","columns-feature","cards-tile","cards-tile","cards-tile","cards-tile","cards-tile"]</t>
   </si>
   <si>
     <t>students</t>
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-27T07:58:41.076Z</t>
+    <t>2026-08-27T20:54:36.898Z</t>
   </si>
   <si>
     <t>Current students - RMIT University</t>

--- a/tools/importer/reports/import-students.report.xlsx
+++ b/tools/importer/reports/import-students.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-27T20:54:36.898Z</t>
+    <t>2026-08-27T23:56:48.807Z</t>
   </si>
   <si>
     <t>Current students - RMIT University</t>

--- a/tools/importer/reports/import-students.report.xlsx
+++ b/tools/importer/reports/import-students.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-27T23:56:48.807Z</t>
+    <t>2026-08-28T01:11:04.164Z</t>
   </si>
   <si>
     <t>Current students - RMIT University</t>

--- a/tools/importer/reports/import-students.report.xlsx
+++ b/tools/importer/reports/import-students.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-08-28T01:11:04.164Z</t>
+    <t>2026-08-28T01:20:35.560Z</t>
   </si>
   <si>
     <t>Current students - RMIT University</t>
